--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_508_Mozambique.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_508_Mozambique.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rb62cc0a0cda44f08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R2c6a9a74e32a4ee5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R8c81d0d1df9d4b59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rfbf49e034d204b3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rf688c009d814465f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R71d4e8af076744f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re072dc8d38754771"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R970164d4dc7445e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R697e6c6d9f284cdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R2e57daef62fb4f8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Racd8387585724378"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R137b38d9142a42b5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ508CommercialTable" displayName="EEZ508CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ508CommercialTable" displayName="EEZ508CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ508FunctionalTable" displayName="EEZ508FunctionalTable" ref="A1:O20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O20"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ508FunctionalTable" displayName="EEZ508FunctionalTable" ref="A1:E20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E20"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ508ValidationTable" displayName="EEZ508ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ508ValidationTable" displayName="EEZ508ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6724,7 +6678,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R642e4ed4bfac48a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42f956330d854235"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6734,20 +6688,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6755,552 +6699,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>22908.469598237498</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.20000402274394</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>158.49078729354895</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>22908.469598237498</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>158.4910515213467</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$91,A2,'Species'!$U$2:$U$91))</x:f>
-        <x:v>3630787.4353694636</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.20000402274394</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>158.49078729354895</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>3630781.382314992</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>6.053054471500218</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0000016671492535</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.000001667149253596971</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>14382.1367778</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.327928189477937</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>212.7787187627683</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>14382.1367778</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>267.05907968368905</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$91,A3,'Species'!$U$2:$U$91))</x:f>
-        <x:v>3840880.211764205</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.327928189477937</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>212.7787187627683</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3060212.6366511732</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>780667.5751130315</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.2551023957496383</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.2551023957496383</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>101.6854434879</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.1500000000000004</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>141.25375446227554</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>101.6854434879</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>141.2537544622754</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$91,A4,'Species'!$U$2:$U$91))</x:f>
-        <x:v>14363.450666827408</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.1500000000000004</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>141.25375446227554</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>14363.450666827423</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>-1.4551915228366852e-11</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>-1.0131211201201597e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>28342.200170209202</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.1599997309251493</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>144.54388751983527</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>28342.200170209202</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>144.54422508163597</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$91,A5,'Species'!$U$2:$U$91))</x:f>
-        <x:v>4096701.3607115005</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.1599997309251493</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>144.54388751983527</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>4096691.793467375</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>9.567244125530124</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0000023353585301</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0000023353585302136093</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>89334.7863511236</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.3201322691035977</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>208.9932545602011</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>89334.7863511236</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>230.68710484545343</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$91,A6,'Species'!$U$2:$U$91))</x:f>
-        <x:v>20608383.225327834</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.3201322691035977</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>208.9932545602011</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>18670367.744961556</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1938015.4803662784</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1038016769053345</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.10380167690533451</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>130378.83013250609</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.6523468925734477</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>449.1039683527105</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>130378.83013250609</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>832.7095643500048</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$91,A7,'Species'!$U$2:$U$91))</x:f>
-        <x:v>108567698.84010243</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.6523468925734477</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>449.1039683527105</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>58553650.00169244</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>50014048.83841</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.8541576628777947</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.8541576628777948</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>67.06136045</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>794.3282347242813</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>67.06136045</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$91,A8,'Species'!$U$2:$U$91))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>53268.73206445723</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.9</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>53268.73206445723</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>8396.116472495902</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.063342405041067</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1157.0240998556985</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>8396.116472495902</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1178.2182564785257</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$91,A9,'Species'!$U$2:$U$91))</x:f>
-        <x:v>9892457.71141475</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.063342405041067</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1157.0240998556985</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>9714509.103873173</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>177948.6075415779</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0183178177753347</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.01831781777533461</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>2327.2678161626</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.273681329137226</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1877.9383423586191</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>2327.2678161626</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1919.3992778919492</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$91,A10,'Species'!$U$2:$U$91))</x:f>
-        <x:v>4466956.165803668</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.273681329137226</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1877.9383423586191</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>4370465.464908957</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>96490.70089471154</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0220779003219331</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.022077900321933235</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1363fc3af3fc425c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e1ae25a7875422b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7310,20 +6895,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7331,1092 +6906,383 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>5057.140841066901</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.809132727655988</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>644.366164500864</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>5057.140841066901</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>644.5276754353642</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$91,A2,'Species'!$U$2:$U$91))</x:f>
-        <x:v>3259467.2306420924</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.809132727655988</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>644.366164500864</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>3258650.4470989523</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>816.7835431401618</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.000250650861883</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0002506508618828116</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>27.9522671861</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>31.622776601683793</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>27.9522671861</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>31.622776601683793</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$91,A3,'Species'!$U$2:$U$91))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>883.9283007366167</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.5</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>31.622776601683793</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>883.9283007366167</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>4602.7173197699</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.148565416803969</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1407.8792780902759</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>4602.7173197699</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1413.3664302171567</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$91,A4,'Species'!$U$2:$U$91))</x:f>
-        <x:v>6505326.147541863</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.148565416803969</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1407.8792780902759</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>6480070.3374112565</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>25255.810130606405</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0038974592582426</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.003897459258242547</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>130.5435104205</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.0021543826342345</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1004.9729737296896</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>130.5435104205</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1061.1408774383976</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$91,A5,'Species'!$U$2:$U$91))</x:f>
-        <x:v>138525.055191498</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.0021543826342345</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1004.9729737296896</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>131192.69986840262</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>7332.355323095369</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0558899643840727</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.05588996438407276</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>2762.8138105309004</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.494461036772582</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>3122.2022816999042</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>2762.8138105309004</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>3129.2356292078034</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$91,A6,'Species'!$U$2:$U$91))</x:f>
-        <x:v>8645495.41278067</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.494461036772582</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>3122.2022816999042</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>8626063.583151584</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>19431.829629085958</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0022526879661589</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.002252687966158768</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2.7077887143</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.5999999999999996</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>398.1071705534969</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2.7077887143</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>398.1071705534973</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$91,A7,'Species'!$U$2:$U$91))</x:f>
-        <x:v>1077.9901035066653</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.5999999999999996</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>398.1071705534969</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1077.9901035066641</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1.1368683772161603e-12</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>1.0546185660869865e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>603.552244</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.4999999999999996</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>316.2277660168376</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>603.552244</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$91,A8,'Species'!$U$2:$U$91))</x:f>
-        <x:v>190859.97779456948</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.4999999999999996</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>316.2277660168376</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>190859.97779456928</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2.0372681319713593e-10</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>1.0674150523920513e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>8393.408683781601</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.063491883445193</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1157.422400755604</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>8393.408683781601</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1178.4699272923692</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$91,A9,'Species'!$U$2:$U$91))</x:f>
-        <x:v>9891379.721311243</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.063491883445193</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1157.422400755604</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>9714719.229305435</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>176660.49200580828</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0181848273569136</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.01818482735691362</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>4014.502693</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.374228546589245</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>236.71650855851803</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>4014.502693</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>429.46316215752336</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$91,A10,'Species'!$U$2:$U$91))</x:f>
-        <x:v>1724081.0210256733</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.374228546589245</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>236.71650855851803</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>950299.0610857281</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>773781.9599399451</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.8142509991074705</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.8142509991074703</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>743.5192607415</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.310588389933166</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>204.4506002445259</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>743.5192607415</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>204.56727186762242</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$91,A11,'Species'!$U$2:$U$91))</x:f>
-        <x:v>152099.70675092007</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.310588389933166</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>204.4506002445259</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>152012.95915196586</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>86.74759895421448</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.000570659234832</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0005706592348320367</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>114085.21212096998</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.3791777443454305</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>239.4295472758789</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>114085.21212096998</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>269.9618446024537</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$91,A12,'Species'!$U$2:$U$91))</x:f>
-        <x:v>30798654.306039266</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.3791777443454305</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>239.4295472758789</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>27315370.688996453</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>3483283.6170428135</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1275210084718343</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.1275210084718344</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>53572.3365109781</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.11772009122907</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1311.3544406080873</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>53572.3365109781</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1392.6636610021642</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$91,A13,'Species'!$U$2:$U$91))</x:f>
-        <x:v>74608246.29381867</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.11772009122907</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1311.3544406080873</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>70252321.3774219</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>4355924.916396767</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0620039997396684</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.06200399973966838</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>36876.51462128649</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.9621708698453335</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>91.65810409960713</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>36876.51462128649</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>236.87175352992156</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$91,A14,'Species'!$U$2:$U$91))</x:f>
-        <x:v>8735004.682415923</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.9621708698453335</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>91.65810409960713</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>3380031.4159885617</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>5354973.266427361</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>2.5842968917675537</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>1.5842968917675537</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>10367.6340848</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.3100000000000005</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>204.17379446695315</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>10367.6340848</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>204.17379446695298</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$91,A15,'Species'!$U$2:$U$91))</x:f>
-        <x:v>2116799.1907385313</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.3100000000000005</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>204.17379446695315</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>2116799.190738533</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>-1.862645149230957e-9</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>0.9999999999999991</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>-8.799347417461436e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>1671.5900951845001</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.0762566073635473</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>119.19460736074785</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>1671.5900951845001</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>121.82808425074651</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$91,A16,'Species'!$U$2:$U$91))</x:f>
-        <x:v>203646.61894885066</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.0762566073635473</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>119.19460736074785</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>199244.52506363162</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>4402.093885219045</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0220939264645448</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.02209392646454487</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>455.6460523056</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.6169915400809916</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>413.9916103156858</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>455.6460523056</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>414.3183263365706</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$91,A17,'Species'!$U$2:$U$91))</x:f>
-        <x:v>188782.5097931217</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.6169915400809916</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>413.9916103156858</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>188633.64292798055</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>148.86686514114263</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0007891851253596</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.0007891851253595272</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>52768.2212191741</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.179725428571762</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>151.26046409989806</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>52768.2212191741</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>151.53907124197517</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$91,A18,'Species'!$U$2:$U$91))</x:f>
-        <x:v>7996447.234644729</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.179725428571762</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>151.26046409989806</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>7981745.631338363</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>14701.60330636613</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0018419032609414</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.0018419032609413033</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>0.8555550744</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.62</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>416.8693834703355</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>0.8555550744</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$91,A19,'Species'!$U$2:$U$91))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>356.654716390045</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.62</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>356.654716390045</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>101.6854434879</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.1500000000000004</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>141.25375446227554</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>101.6854434879</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>141.2537544622754</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$91,A20,'Species'!$U$2:$U$91))</x:f>
-        <x:v>14363.450666827408</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.1500000000000004</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>141.25375446227554</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>14363.450666827423</x:v>
       </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>-1.4551915228366852e-11</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>-1.0131211201201597e-15</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G20">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O20">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffdfebc41a3b45d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ff2e99e856e4844"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8591,7 +7457,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8690,7 +7556,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>155171497.13322508</x:v>
+        <x:v>102164310.31060095</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8704,7 +7570,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>155171497.13322508</x:v>
+        <x:v>140954696.79113078</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8718,7 +7584,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-53007186.82262413</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8732,7 +7598,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-14216800.342094302</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8743,9 +7609,9 @@
         <x:v>EEZ_508</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8757,47 +7623,19 @@
         <x:v>EEZ_508</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_508</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_508</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49130f460ce54857"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref702c1880244a14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8844,7 +7682,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
